--- a/lab13/wyniki.xlsx
+++ b/lab13/wyniki.xlsx
@@ -8,17 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Rownolegle\lab13\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D56E3CFD-7F62-4DCD-B828-4828F4AC3818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79FFCB94-560F-46B5-8D82-19CE1EFEAFE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F88E4DAB-D45D-44FA-B043-7D7CF45B79E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$C$15:$F$15</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$C$8:$F$8</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="16">
   <si>
     <t>Ilosc</t>
   </si>
@@ -63,13 +59,31 @@
     <t>mat_vec</t>
   </si>
   <si>
-    <t>mam 6</t>
-  </si>
-  <si>
     <t>przyspieszenie</t>
   </si>
   <si>
     <t>wydajnosc</t>
+  </si>
+  <si>
+    <t>czas 4</t>
+  </si>
+  <si>
+    <t>czas 5</t>
+  </si>
+  <si>
+    <t>czas 6</t>
+  </si>
+  <si>
+    <t>czas 7</t>
+  </si>
+  <si>
+    <t>czas 8</t>
+  </si>
+  <si>
+    <t>czas 9</t>
+  </si>
+  <si>
+    <t>czas 10</t>
   </si>
 </sst>
 </file>
@@ -255,16 +269,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.20328300000000002</c:v>
+                  <c:v>0.190056</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.14180200000000001</c:v>
+                  <c:v>0.13877533333333333</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.11376866666666667</c:v>
+                  <c:v>8.981933333333332E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.5967999999999994E-2</c:v>
+                  <c:v>6.8139666666666668E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -681,21 +695,21 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$C$15:$F$15</c:f>
+              <c:f>Sheet1!$C$22:$F$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.12123966666666668</c:v>
+                  <c:v>6.5051999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.10383866666666668</c:v>
+                  <c:v>3.5844599999999997E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.8767666666666666E-2</c:v>
+                  <c:v>3.5802800000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.6107999999999994E-2</c:v>
+                  <c:v>2.9370299999999998E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1122,13 +1136,13 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.4335693431686436</c:v>
+                  <c:v>1.369522921940979</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.7868100765881645</c:v>
+                  <c:v>2.1159809692048488</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.67590301179444</c:v>
+                  <c:v>2.7892123530591579</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1648,7 +1662,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$C$16:$F$16</c:f>
+              <c:f>Sheet1!$C$23:$F$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -1656,13 +1670,13 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.1675772672992719</c:v>
+                  <c:v>1.8148340335782798</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.1273397934705041</c:v>
+                  <c:v>1.8169528640218082</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.357695432221854</c:v>
+                  <c:v>2.2148905527011982</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2198,13 +2212,13 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.7167846715843218</c:v>
+                  <c:v>0.68476146097048951</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.44670251914704112</c:v>
+                  <c:v>0.5289952423012122</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.44598383529907332</c:v>
+                  <c:v>0.46486872550985964</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2724,7 +2738,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$C$17:$F$17</c:f>
+              <c:f>Sheet1!$C$24:$F$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -2732,13 +2746,13 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.58378863364963596</c:v>
+                  <c:v>0.90741701678913989</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.78183494836762601</c:v>
+                  <c:v>0.45423821600545206</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.55961590537030903</c:v>
+                  <c:v>0.36914842545019971</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6933,19 +6947,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6043E229-BA14-4BA3-B3AE-C550CE3683A6}">
-  <dimension ref="B1:G17"/>
+  <dimension ref="B1:F24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="13.08984375" bestFit="1" customWidth="1"/>
     <col min="3" max="7" width="11.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -6961,98 +6975,82 @@
       <c r="F2">
         <v>6</v>
       </c>
-      <c r="G2">
-        <v>8</v>
-      </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>1</v>
       </c>
       <c r="C3">
-        <v>0.19151599999999999</v>
+        <v>0.18398100000000001</v>
       </c>
       <c r="D3">
-        <v>0.14530000000000001</v>
+        <v>0.159716</v>
       </c>
       <c r="E3">
-        <v>0.116508</v>
+        <v>8.6363999999999996E-2</v>
       </c>
       <c r="F3">
-        <v>7.3615E-2</v>
-      </c>
-      <c r="G3">
-        <v>7.0855000000000001E-2</v>
+        <v>7.6255000000000003E-2</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>2</v>
       </c>
       <c r="C4">
-        <v>0.221665</v>
+        <v>0.19551099999999999</v>
       </c>
       <c r="D4">
-        <v>0.12667300000000001</v>
+        <v>0.121031</v>
       </c>
       <c r="E4">
-        <v>0.13300300000000001</v>
+        <v>8.8581999999999994E-2</v>
       </c>
       <c r="F4">
-        <v>8.8244000000000003E-2</v>
-      </c>
-      <c r="G4">
-        <v>7.1349999999999997E-2</v>
+        <v>6.5636E-2</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>3</v>
       </c>
       <c r="C5">
-        <v>0.19666800000000001</v>
+        <v>0.19067600000000001</v>
       </c>
       <c r="D5">
-        <v>0.15343300000000001</v>
+        <v>0.13557900000000001</v>
       </c>
       <c r="E5">
-        <v>9.1795000000000002E-2</v>
+        <v>9.4511999999999999E-2</v>
       </c>
       <c r="F5">
-        <v>6.6045000000000006E-2</v>
-      </c>
-      <c r="G5">
-        <v>4.7698999999999998E-2</v>
+        <v>6.2528E-2</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>4</v>
       </c>
       <c r="C6">
         <f>AVERAGE(C3:C5)</f>
-        <v>0.20328300000000002</v>
+        <v>0.190056</v>
       </c>
       <c r="D6">
         <f t="shared" ref="D6:F6" si="0">AVERAGE(D3:D5)</f>
-        <v>0.14180200000000001</v>
+        <v>0.13877533333333333</v>
       </c>
       <c r="E6">
         <f t="shared" si="0"/>
-        <v>0.11376866666666667</v>
+        <v>8.981933333333332E-2</v>
       </c>
       <c r="F6">
         <f t="shared" si="0"/>
-        <v>7.5967999999999994E-2</v>
-      </c>
-      <c r="G6">
-        <f>AVERAGE(G3:G5)</f>
-        <v>6.3301333333333334E-2</v>
+        <v>6.8139666666666668E-2</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7">
         <f>$C$6/C6</f>
@@ -7060,24 +7058,20 @@
       </c>
       <c r="D7">
         <f t="shared" ref="D7:G7" si="1">$C$6/D6</f>
-        <v>1.4335693431686436</v>
+        <v>1.369522921940979</v>
       </c>
       <c r="E7">
         <f t="shared" si="1"/>
-        <v>1.7868100765881645</v>
+        <v>2.1159809692048488</v>
       </c>
       <c r="F7">
         <f t="shared" si="1"/>
-        <v>2.67590301179444</v>
-      </c>
-      <c r="G7">
-        <f t="shared" si="1"/>
-        <v>3.2113541578903027</v>
+        <v>2.7892123530591579</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8">
         <f>C7/C2</f>
@@ -7085,27 +7079,23 @@
       </c>
       <c r="D8">
         <f t="shared" ref="D8:G8" si="2">D7/D2</f>
-        <v>0.7167846715843218</v>
+        <v>0.68476146097048951</v>
       </c>
       <c r="E8">
         <f t="shared" si="2"/>
-        <v>0.44670251914704112</v>
+        <v>0.5289952423012122</v>
       </c>
       <c r="F8">
         <f t="shared" si="2"/>
-        <v>0.44598383529907332</v>
-      </c>
-      <c r="G8">
-        <f t="shared" si="2"/>
-        <v>0.40141926973628783</v>
+        <v>0.46486872550985964</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>0</v>
       </c>
@@ -7121,122 +7111,238 @@
       <c r="F11">
         <v>6</v>
       </c>
-      <c r="G11" t="s">
-        <v>7</v>
-      </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>1</v>
       </c>
       <c r="C12">
-        <v>0.115317</v>
+        <v>6.1020999999999999E-2</v>
       </c>
       <c r="D12">
-        <v>0.126635</v>
+        <v>3.4979999999999997E-2</v>
       </c>
       <c r="E12">
-        <v>4.0923000000000001E-2</v>
+        <v>3.3356999999999998E-2</v>
       </c>
       <c r="F12">
-        <v>3.3891999999999999E-2</v>
+        <v>2.8809000000000001E-2</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>2</v>
       </c>
       <c r="C13">
-        <v>0.12848399999999999</v>
+        <v>6.3031000000000004E-2</v>
       </c>
       <c r="D13">
-        <v>7.4881000000000003E-2</v>
+        <v>3.5237999999999998E-2</v>
       </c>
       <c r="E13">
-        <v>3.9649999999999998E-2</v>
+        <v>3.8280000000000002E-2</v>
       </c>
       <c r="F13">
-        <v>3.6479999999999999E-2</v>
+        <v>2.6880999999999999E-2</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>3</v>
       </c>
       <c r="C14">
-        <v>0.119918</v>
+        <v>6.7124000000000003E-2</v>
       </c>
       <c r="D14">
-        <v>0.11</v>
+        <v>3.3114999999999999E-2</v>
       </c>
       <c r="E14">
-        <v>3.5729999999999998E-2</v>
+        <v>3.4582000000000002E-2</v>
       </c>
       <c r="F14">
-        <v>3.7952E-2</v>
+        <v>2.5472999999999999E-2</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15">
-        <f>AVERAGE(C12:C14)</f>
-        <v>0.12123966666666668</v>
+        <v>6.0754000000000002E-2</v>
       </c>
       <c r="D15">
-        <f t="shared" ref="D15:F15" si="3">AVERAGE(D12:D14)</f>
-        <v>0.10383866666666668</v>
+        <v>4.4982000000000001E-2</v>
       </c>
       <c r="E15">
-        <f t="shared" si="3"/>
-        <v>3.8767666666666666E-2</v>
+        <v>5.5874E-2</v>
       </c>
       <c r="F15">
-        <f t="shared" si="3"/>
-        <v>3.6107999999999994E-2</v>
+        <v>2.9569999999999999E-2</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C16">
-        <f>$C$15/C15</f>
-        <v>1</v>
+        <v>6.2175000000000001E-2</v>
       </c>
       <c r="D16">
-        <f t="shared" ref="D16:F16" si="4">$C$15/D15</f>
-        <v>1.1675772672992719</v>
+        <v>3.0329999999999999E-2</v>
       </c>
       <c r="E16">
-        <f t="shared" si="4"/>
-        <v>3.1273397934705041</v>
+        <v>3.5999000000000003E-2</v>
       </c>
       <c r="F16">
-        <f t="shared" si="4"/>
-        <v>3.357695432221854</v>
+        <v>2.7479E-2</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C17">
-        <f>C16/C11</f>
+        <v>6.9001000000000007E-2</v>
+      </c>
+      <c r="D17">
+        <v>3.0932999999999999E-2</v>
+      </c>
+      <c r="E17">
+        <v>3.1125E-2</v>
+      </c>
+      <c r="F17">
+        <v>3.3683999999999999E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18">
+        <v>5.8028999999999997E-2</v>
+      </c>
+      <c r="D18">
+        <v>3.9373999999999999E-2</v>
+      </c>
+      <c r="E18">
+        <v>3.3453999999999998E-2</v>
+      </c>
+      <c r="F18">
+        <v>2.9961999999999999E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19">
+        <v>7.8172000000000005E-2</v>
+      </c>
+      <c r="D19">
+        <v>3.5575000000000002E-2</v>
+      </c>
+      <c r="E19">
+        <v>3.5691000000000001E-2</v>
+      </c>
+      <c r="F19">
+        <v>3.0006000000000001E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20">
+        <v>6.9744E-2</v>
+      </c>
+      <c r="D20">
+        <v>3.5602000000000002E-2</v>
+      </c>
+      <c r="E20">
+        <v>2.7140999999999998E-2</v>
+      </c>
+      <c r="F20">
+        <v>3.3839000000000001E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21">
+        <v>6.1469000000000003E-2</v>
+      </c>
+      <c r="D21">
+        <v>3.8316999999999997E-2</v>
+      </c>
+      <c r="E21">
+        <v>3.2524999999999998E-2</v>
+      </c>
+      <c r="F21">
+        <v>2.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22">
+        <f>AVERAGE(C12:C21)</f>
+        <v>6.5051999999999999E-2</v>
+      </c>
+      <c r="D22">
+        <f t="shared" ref="D22:F22" si="3">AVERAGE(D12:D21)</f>
+        <v>3.5844599999999997E-2</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="3"/>
+        <v>3.5802800000000003E-2</v>
+      </c>
+      <c r="F22">
+        <f>AVERAGE(F12:F21)</f>
+        <v>2.9370299999999998E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23">
+        <f>$C$22/C22</f>
         <v>1</v>
       </c>
-      <c r="D17">
-        <f t="shared" ref="D17:F17" si="5">D16/D11</f>
-        <v>0.58378863364963596</v>
-      </c>
-      <c r="E17">
-        <f t="shared" si="5"/>
-        <v>0.78183494836762601</v>
-      </c>
-      <c r="F17">
-        <f t="shared" si="5"/>
-        <v>0.55961590537030903</v>
+      <c r="D23">
+        <f>$C$22/D22</f>
+        <v>1.8148340335782798</v>
+      </c>
+      <c r="E23">
+        <f>$C$22/E22</f>
+        <v>1.8169528640218082</v>
+      </c>
+      <c r="F23">
+        <f>$C$22/F22</f>
+        <v>2.2148905527011982</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24">
+        <f>C23/C11</f>
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <f>D23/D11</f>
+        <v>0.90741701678913989</v>
+      </c>
+      <c r="E24">
+        <f>E23/E11</f>
+        <v>0.45423821600545206</v>
+      </c>
+      <c r="F24">
+        <f>F23/F11</f>
+        <v>0.36914842545019971</v>
       </c>
     </row>
   </sheetData>
